--- a/data/XRD/2 Round/Mo_400deg_25Se_400Sb_35Se.xlsx
+++ b/data/XRD/2 Round/Mo_400deg_25Se_400Sb_35Se.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fbdd27f2520478cf/Ambiente de Trabalho/TESE/Data_Analysis/data/XRD/2 Round/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{DC294F50-4EE4-47F8-8B15-1CECD2201D7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFB6D5D0-7351-4DBC-9C90-2B000FE6517E}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{DC294F50-4EE4-47F8-8B15-1CECD2201D7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24E32861-F20F-40C3-92E0-B0424F72E960}"/>
   <bookViews>
-    <workbookView xWindow="1980" yWindow="4044" windowWidth="17280" windowHeight="8880" xr2:uid="{BD6B42E7-8F25-4A4F-8CC8-88E838C5844F}"/>
+    <workbookView xWindow="3984" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{BD6B42E7-8F25-4A4F-8CC8-88E838C5844F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="415">
   <si>
     <t>No.</t>
   </si>
@@ -131,9 +131,6 @@
     <t>Profile fitting</t>
   </si>
   <si>
-    <t>96-900-8581</t>
-  </si>
-  <si>
     <t>100,00</t>
   </si>
   <si>
@@ -170,9 +167,6 @@
     <t>302,01</t>
   </si>
   <si>
-    <t>00-015-0861; 01-072-1184</t>
-  </si>
-  <si>
     <t>3,48</t>
   </si>
   <si>
@@ -221,9 +215,6 @@
     <t>375(29)</t>
   </si>
   <si>
-    <t>00-015-0861; 01-085-0455; 01-072-1184</t>
-  </si>
-  <si>
     <t>4,33</t>
   </si>
   <si>
@@ -344,9 +335,6 @@
     <t>4999(49)</t>
   </si>
   <si>
-    <t>00-015-0861; 96-901-3009; 01-072-1184</t>
-  </si>
-  <si>
     <t>57,63</t>
   </si>
   <si>
@@ -587,9 +575,6 @@
     <t>8674(27)</t>
   </si>
   <si>
-    <t>00-001-1205; 96-901-3009</t>
-  </si>
-  <si>
     <t>0,469231</t>
   </si>
   <si>
@@ -725,9 +710,6 @@
     <t>71(14)</t>
   </si>
   <si>
-    <t>00-015-0861; 96-901-3014; 01-085-0455; 01-072-1184</t>
-  </si>
-  <si>
     <t>0,82</t>
   </si>
   <si>
@@ -845,9 +827,6 @@
     <t>252(15)</t>
   </si>
   <si>
-    <t>00-015-0861; 96-900-8581; 01-072-1184</t>
-  </si>
-  <si>
     <t>2,90</t>
   </si>
   <si>
@@ -872,9 +851,6 @@
     <t>665(16)</t>
   </si>
   <si>
-    <t>00-015-0861; 96-901-1653</t>
-  </si>
-  <si>
     <t>7,66</t>
   </si>
   <si>
@@ -896,9 +872,6 @@
     <t>127(16)</t>
   </si>
   <si>
-    <t>00-015-0861; 01-072-1184; 01-073-1789</t>
-  </si>
-  <si>
     <t>1,46</t>
   </si>
   <si>
@@ -923,9 +896,6 @@
     <t>867(46)</t>
   </si>
   <si>
-    <t>00-015-0861; 96-901-1653; 01-085-0455; 01-072-1184</t>
-  </si>
-  <si>
     <t>10,00</t>
   </si>
   <si>
@@ -950,9 +920,6 @@
     <t>224(28)</t>
   </si>
   <si>
-    <t>00-015-0861; 96-901-3009; 96-901-1653; 01-072-1184</t>
-  </si>
-  <si>
     <t>2,59</t>
   </si>
   <si>
@@ -974,9 +941,6 @@
     <t>135(10)</t>
   </si>
   <si>
-    <t>96-901-1653; 01-072-1184; 01-073-1789</t>
-  </si>
-  <si>
     <t>1,55</t>
   </si>
   <si>
@@ -1001,9 +965,6 @@
     <t>92(17)</t>
   </si>
   <si>
-    <t>01-072-1184</t>
-  </si>
-  <si>
     <t>1,07</t>
   </si>
   <si>
@@ -1028,9 +989,6 @@
     <t>253(13)</t>
   </si>
   <si>
-    <t>01-085-0455; 01-072-1184</t>
-  </si>
-  <si>
     <t>2,91</t>
   </si>
   <si>
@@ -1055,9 +1013,6 @@
     <t>206(14)</t>
   </si>
   <si>
-    <t>00-047-1514; 01-085-0455</t>
-  </si>
-  <si>
     <t>2,38</t>
   </si>
   <si>
@@ -1103,9 +1058,6 @@
     <t>202(13)</t>
   </si>
   <si>
-    <t>01-073-1789</t>
-  </si>
-  <si>
     <t>2,33</t>
   </si>
   <si>
@@ -1202,9 +1154,6 @@
     <t>125(13)</t>
   </si>
   <si>
-    <t>96-901-3014</t>
-  </si>
-  <si>
     <t>1,44</t>
   </si>
   <si>
@@ -1229,9 +1178,6 @@
     <t>81(8)</t>
   </si>
   <si>
-    <t>96-900-8581; 01-085-0455; 01-072-1184</t>
-  </si>
-  <si>
     <t>0,252700</t>
   </si>
   <si>
@@ -1302,6 +1248,42 @@
   </si>
   <si>
     <t>0,120886</t>
+  </si>
+  <si>
+    <t>00-029-0914</t>
+  </si>
+  <si>
+    <t>00-001-1205</t>
+  </si>
+  <si>
+    <t>00-015-0861; 00-029-0914</t>
+  </si>
+  <si>
+    <t>34,3930</t>
+  </si>
+  <si>
+    <t>0,2581</t>
+  </si>
+  <si>
+    <t>39,77</t>
+  </si>
+  <si>
+    <t>1046,45</t>
+  </si>
+  <si>
+    <t>2,60545</t>
+  </si>
+  <si>
+    <t>115,55</t>
+  </si>
+  <si>
+    <t>1,33</t>
+  </si>
+  <si>
+    <t>Manual input</t>
+  </si>
+  <si>
+    <t>0,344168</t>
   </si>
 </sst>
 </file>
@@ -1677,7 +1659,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA4B8A9B-7994-4D7C-8BA3-BE0666BFC9CE}">
-  <dimension ref="A1:W48"/>
+  <dimension ref="A1:W49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.3">
@@ -1756,43 +1738,43 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" t="s">
         <v>38</v>
       </c>
-      <c r="C2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" t="s">
         <v>39</v>
       </c>
-      <c r="M2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>40</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>41</v>
-      </c>
-      <c r="P2" t="s">
-        <v>42</v>
       </c>
       <c r="R2" t="b">
         <v>1</v>
       </c>
       <c r="S2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="U2" t="s">
         <v>26</v>
@@ -1801,7 +1783,7 @@
         <v>27</v>
       </c>
       <c r="W2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
@@ -1809,34 +1791,34 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" t="s">
         <v>45</v>
       </c>
-      <c r="C3" t="s">
+      <c r="M3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3" t="s">
         <v>46</v>
       </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="O3" t="s">
         <v>47</v>
       </c>
-      <c r="M3" t="s">
-        <v>25</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="P3" t="s">
         <v>48</v>
-      </c>
-      <c r="O3" t="s">
-        <v>49</v>
-      </c>
-      <c r="P3" t="s">
-        <v>50</v>
       </c>
       <c r="Q3" t="s">
         <v>28</v>
@@ -1845,19 +1827,19 @@
         <v>1</v>
       </c>
       <c r="S3" t="s">
+        <v>49</v>
+      </c>
+      <c r="T3" t="s">
+        <v>50</v>
+      </c>
+      <c r="U3" t="s">
+        <v>29</v>
+      </c>
+      <c r="V3" t="s">
+        <v>27</v>
+      </c>
+      <c r="W3" t="s">
         <v>51</v>
-      </c>
-      <c r="T3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U3" t="s">
-        <v>29</v>
-      </c>
-      <c r="V3" t="s">
-        <v>27</v>
-      </c>
-      <c r="W3" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.3">
@@ -1865,34 +1847,34 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" t="s">
         <v>54</v>
       </c>
-      <c r="C4" t="s">
+      <c r="M4" t="s">
+        <v>25</v>
+      </c>
+      <c r="N4" t="s">
         <v>55</v>
       </c>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
-      <c r="J4" t="s">
-        <v>24</v>
-      </c>
-      <c r="K4" t="s">
-        <v>24</v>
-      </c>
-      <c r="L4" t="s">
+      <c r="O4" t="s">
         <v>56</v>
       </c>
-      <c r="M4" t="s">
-        <v>25</v>
-      </c>
-      <c r="N4" t="s">
+      <c r="P4" t="s">
         <v>57</v>
-      </c>
-      <c r="O4" t="s">
-        <v>58</v>
-      </c>
-      <c r="P4" t="s">
-        <v>59</v>
       </c>
       <c r="Q4" t="s">
         <v>28</v>
@@ -1901,10 +1883,10 @@
         <v>1</v>
       </c>
       <c r="S4" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="T4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="U4" t="s">
         <v>29</v>
@@ -1913,7 +1895,7 @@
         <v>27</v>
       </c>
       <c r="W4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.3">
@@ -1921,34 +1903,34 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" t="s">
+        <v>62</v>
+      </c>
+      <c r="M5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N5" t="s">
         <v>63</v>
       </c>
-      <c r="C5" t="s">
+      <c r="O5" t="s">
         <v>64</v>
       </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="P5" t="s">
         <v>65</v>
-      </c>
-      <c r="M5" t="s">
-        <v>25</v>
-      </c>
-      <c r="N5" t="s">
-        <v>66</v>
-      </c>
-      <c r="O5" t="s">
-        <v>67</v>
-      </c>
-      <c r="P5" t="s">
-        <v>68</v>
       </c>
       <c r="Q5" t="s">
         <v>28</v>
@@ -1957,10 +1939,10 @@
         <v>1</v>
       </c>
       <c r="S5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="U5" t="s">
         <v>29</v>
@@ -1969,7 +1951,7 @@
         <v>27</v>
       </c>
       <c r="W5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.3">
@@ -1977,34 +1959,34 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" t="s">
+        <v>70</v>
+      </c>
+      <c r="M6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N6" t="s">
         <v>71</v>
       </c>
-      <c r="C6" t="s">
+      <c r="O6" t="s">
         <v>72</v>
       </c>
-      <c r="D6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L6" t="s">
+      <c r="P6" t="s">
         <v>73</v>
-      </c>
-      <c r="M6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N6" t="s">
-        <v>74</v>
-      </c>
-      <c r="O6" t="s">
-        <v>75</v>
-      </c>
-      <c r="P6" t="s">
-        <v>76</v>
       </c>
       <c r="Q6" t="s">
         <v>28</v>
@@ -2013,10 +1995,10 @@
         <v>1</v>
       </c>
       <c r="S6" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="U6" t="s">
         <v>29</v>
@@ -2025,7 +2007,7 @@
         <v>27</v>
       </c>
       <c r="W6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.3">
@@ -2033,34 +2015,34 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" t="s">
+        <v>78</v>
+      </c>
+      <c r="M7" t="s">
+        <v>25</v>
+      </c>
+      <c r="N7" t="s">
         <v>79</v>
       </c>
-      <c r="C7" t="s">
+      <c r="O7" t="s">
         <v>80</v>
       </c>
-      <c r="D7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J7" t="s">
-        <v>24</v>
-      </c>
-      <c r="K7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L7" t="s">
+      <c r="P7" t="s">
         <v>81</v>
-      </c>
-      <c r="M7" t="s">
-        <v>25</v>
-      </c>
-      <c r="N7" t="s">
-        <v>82</v>
-      </c>
-      <c r="O7" t="s">
-        <v>83</v>
-      </c>
-      <c r="P7" t="s">
-        <v>84</v>
       </c>
       <c r="Q7" t="s">
         <v>28</v>
@@ -2069,10 +2051,10 @@
         <v>1</v>
       </c>
       <c r="S7" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T7" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="U7" t="s">
         <v>29</v>
@@ -2081,7 +2063,7 @@
         <v>27</v>
       </c>
       <c r="W7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.3">
@@ -2089,34 +2071,34 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" t="s">
+        <v>86</v>
+      </c>
+      <c r="M8" t="s">
+        <v>25</v>
+      </c>
+      <c r="N8" t="s">
         <v>87</v>
       </c>
-      <c r="C8" t="s">
+      <c r="O8" t="s">
         <v>88</v>
       </c>
-      <c r="D8" t="s">
-        <v>23</v>
-      </c>
-      <c r="J8" t="s">
-        <v>24</v>
-      </c>
-      <c r="K8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L8" t="s">
+      <c r="P8" t="s">
         <v>89</v>
-      </c>
-      <c r="M8" t="s">
-        <v>25</v>
-      </c>
-      <c r="N8" t="s">
-        <v>90</v>
-      </c>
-      <c r="O8" t="s">
-        <v>91</v>
-      </c>
-      <c r="P8" t="s">
-        <v>92</v>
       </c>
       <c r="Q8" t="s">
         <v>28</v>
@@ -2125,10 +2107,10 @@
         <v>1</v>
       </c>
       <c r="S8" t="s">
-        <v>30</v>
+        <v>403</v>
       </c>
       <c r="T8" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="U8" t="s">
         <v>29</v>
@@ -2137,7 +2119,7 @@
         <v>27</v>
       </c>
       <c r="W8" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.3">
@@ -2145,34 +2127,34 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="J9" t="s">
+        <v>24</v>
+      </c>
+      <c r="K9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" t="s">
+        <v>94</v>
+      </c>
+      <c r="M9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N9" t="s">
         <v>95</v>
       </c>
-      <c r="C9" t="s">
+      <c r="O9" t="s">
         <v>96</v>
       </c>
-      <c r="D9" t="s">
-        <v>23</v>
-      </c>
-      <c r="J9" t="s">
-        <v>24</v>
-      </c>
-      <c r="K9" t="s">
-        <v>24</v>
-      </c>
-      <c r="L9" t="s">
+      <c r="P9" t="s">
         <v>97</v>
-      </c>
-      <c r="M9" t="s">
-        <v>25</v>
-      </c>
-      <c r="N9" t="s">
-        <v>98</v>
-      </c>
-      <c r="O9" t="s">
-        <v>99</v>
-      </c>
-      <c r="P9" t="s">
-        <v>100</v>
       </c>
       <c r="Q9" t="s">
         <v>28</v>
@@ -2181,10 +2163,10 @@
         <v>1</v>
       </c>
       <c r="S9" t="s">
-        <v>101</v>
+        <v>49</v>
       </c>
       <c r="T9" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="U9" t="s">
         <v>29</v>
@@ -2193,7 +2175,7 @@
         <v>27</v>
       </c>
       <c r="W9" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.3">
@@ -2201,34 +2183,34 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" t="s">
+        <v>102</v>
+      </c>
+      <c r="M10" t="s">
+        <v>25</v>
+      </c>
+      <c r="N10" t="s">
+        <v>103</v>
+      </c>
+      <c r="O10" t="s">
         <v>104</v>
       </c>
-      <c r="C10" t="s">
+      <c r="P10" t="s">
         <v>105</v>
-      </c>
-      <c r="D10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J10" t="s">
-        <v>24</v>
-      </c>
-      <c r="K10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L10" t="s">
-        <v>106</v>
-      </c>
-      <c r="M10" t="s">
-        <v>25</v>
-      </c>
-      <c r="N10" t="s">
-        <v>107</v>
-      </c>
-      <c r="O10" t="s">
-        <v>108</v>
-      </c>
-      <c r="P10" t="s">
-        <v>109</v>
       </c>
       <c r="Q10" t="s">
         <v>28</v>
@@ -2237,10 +2219,10 @@
         <v>1</v>
       </c>
       <c r="S10" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="U10" t="s">
         <v>29</v>
@@ -2249,7 +2231,7 @@
         <v>27</v>
       </c>
       <c r="W10" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.3">
@@ -2257,34 +2239,34 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J11" t="s">
+        <v>24</v>
+      </c>
+      <c r="K11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" t="s">
+        <v>110</v>
+      </c>
+      <c r="M11" t="s">
+        <v>25</v>
+      </c>
+      <c r="N11" t="s">
+        <v>111</v>
+      </c>
+      <c r="O11" t="s">
         <v>112</v>
       </c>
-      <c r="C11" t="s">
+      <c r="P11" t="s">
         <v>113</v>
-      </c>
-      <c r="D11" t="s">
-        <v>23</v>
-      </c>
-      <c r="J11" t="s">
-        <v>24</v>
-      </c>
-      <c r="K11" t="s">
-        <v>24</v>
-      </c>
-      <c r="L11" t="s">
-        <v>114</v>
-      </c>
-      <c r="M11" t="s">
-        <v>25</v>
-      </c>
-      <c r="N11" t="s">
-        <v>115</v>
-      </c>
-      <c r="O11" t="s">
-        <v>116</v>
-      </c>
-      <c r="P11" t="s">
-        <v>117</v>
       </c>
       <c r="Q11" t="s">
         <v>28</v>
@@ -2293,10 +2275,10 @@
         <v>1</v>
       </c>
       <c r="S11" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T11" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="U11" t="s">
         <v>29</v>
@@ -2305,7 +2287,7 @@
         <v>27</v>
       </c>
       <c r="W11" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.3">
@@ -2313,34 +2295,34 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C12" t="s">
+        <v>117</v>
+      </c>
+      <c r="D12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J12" t="s">
+        <v>24</v>
+      </c>
+      <c r="K12" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" t="s">
+        <v>118</v>
+      </c>
+      <c r="M12" t="s">
+        <v>25</v>
+      </c>
+      <c r="N12" t="s">
+        <v>119</v>
+      </c>
+      <c r="O12" t="s">
         <v>120</v>
       </c>
-      <c r="C12" t="s">
+      <c r="P12" t="s">
         <v>121</v>
-      </c>
-      <c r="D12" t="s">
-        <v>23</v>
-      </c>
-      <c r="J12" t="s">
-        <v>24</v>
-      </c>
-      <c r="K12" t="s">
-        <v>24</v>
-      </c>
-      <c r="L12" t="s">
-        <v>122</v>
-      </c>
-      <c r="M12" t="s">
-        <v>25</v>
-      </c>
-      <c r="N12" t="s">
-        <v>123</v>
-      </c>
-      <c r="O12" t="s">
-        <v>124</v>
-      </c>
-      <c r="P12" t="s">
-        <v>125</v>
       </c>
       <c r="Q12" t="s">
         <v>28</v>
@@ -2349,10 +2331,10 @@
         <v>1</v>
       </c>
       <c r="S12" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T12" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="U12" t="s">
         <v>29</v>
@@ -2361,7 +2343,7 @@
         <v>27</v>
       </c>
       <c r="W12" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.3">
@@ -2369,34 +2351,34 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>124</v>
+      </c>
+      <c r="C13" t="s">
+        <v>125</v>
+      </c>
+      <c r="D13" t="s">
+        <v>23</v>
+      </c>
+      <c r="J13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K13" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" t="s">
+        <v>126</v>
+      </c>
+      <c r="M13" t="s">
+        <v>25</v>
+      </c>
+      <c r="N13" t="s">
+        <v>127</v>
+      </c>
+      <c r="O13" t="s">
         <v>128</v>
       </c>
-      <c r="C13" t="s">
+      <c r="P13" t="s">
         <v>129</v>
-      </c>
-      <c r="D13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J13" t="s">
-        <v>24</v>
-      </c>
-      <c r="K13" t="s">
-        <v>24</v>
-      </c>
-      <c r="L13" t="s">
-        <v>130</v>
-      </c>
-      <c r="M13" t="s">
-        <v>25</v>
-      </c>
-      <c r="N13" t="s">
-        <v>131</v>
-      </c>
-      <c r="O13" t="s">
-        <v>132</v>
-      </c>
-      <c r="P13" t="s">
-        <v>133</v>
       </c>
       <c r="Q13" t="s">
         <v>28</v>
@@ -2405,10 +2387,10 @@
         <v>1</v>
       </c>
       <c r="S13" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T13" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="U13" t="s">
         <v>29</v>
@@ -2417,7 +2399,7 @@
         <v>27</v>
       </c>
       <c r="W13" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.3">
@@ -2425,10 +2407,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>136</v>
+        <v>406</v>
       </c>
       <c r="C14" t="s">
-        <v>137</v>
+        <v>407</v>
       </c>
       <c r="D14" t="s">
         <v>23</v>
@@ -2440,40 +2422,37 @@
         <v>24</v>
       </c>
       <c r="L14" t="s">
-        <v>138</v>
+        <v>408</v>
       </c>
       <c r="M14" t="s">
         <v>25</v>
       </c>
       <c r="N14" t="s">
-        <v>139</v>
+        <v>409</v>
       </c>
       <c r="O14" t="s">
-        <v>140</v>
+        <v>410</v>
       </c>
       <c r="P14" t="s">
-        <v>141</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>28</v>
+        <v>411</v>
       </c>
       <c r="R14" t="b">
         <v>1</v>
       </c>
       <c r="S14" t="s">
-        <v>43</v>
+        <v>405</v>
       </c>
       <c r="T14" t="s">
-        <v>142</v>
+        <v>412</v>
       </c>
       <c r="U14" t="s">
-        <v>29</v>
+        <v>413</v>
       </c>
       <c r="V14" t="s">
         <v>27</v>
       </c>
       <c r="W14" t="s">
-        <v>143</v>
+        <v>414</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.3">
@@ -2481,10 +2460,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="C15" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="D15" t="s">
         <v>23</v>
@@ -2496,19 +2475,19 @@
         <v>24</v>
       </c>
       <c r="L15" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="M15" t="s">
         <v>25</v>
       </c>
       <c r="N15" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="O15" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="P15" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="Q15" t="s">
         <v>28</v>
@@ -2517,10 +2496,10 @@
         <v>1</v>
       </c>
       <c r="S15" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T15" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="U15" t="s">
         <v>29</v>
@@ -2529,7 +2508,7 @@
         <v>27</v>
       </c>
       <c r="W15" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.3">
@@ -2537,10 +2516,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="C16" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="D16" t="s">
         <v>23</v>
@@ -2552,19 +2531,19 @@
         <v>24</v>
       </c>
       <c r="L16" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="M16" t="s">
         <v>25</v>
       </c>
       <c r="N16" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="O16" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="P16" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="Q16" t="s">
         <v>28</v>
@@ -2573,10 +2552,10 @@
         <v>1</v>
       </c>
       <c r="S16" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="T16" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="U16" t="s">
         <v>29</v>
@@ -2585,7 +2564,7 @@
         <v>27</v>
       </c>
       <c r="W16" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.3">
@@ -2593,10 +2572,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="C17" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="D17" t="s">
         <v>23</v>
@@ -2608,19 +2587,19 @@
         <v>24</v>
       </c>
       <c r="L17" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="M17" t="s">
         <v>25</v>
       </c>
       <c r="N17" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="O17" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="P17" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="Q17" t="s">
         <v>28</v>
@@ -2629,10 +2608,10 @@
         <v>1</v>
       </c>
       <c r="S17" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T17" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="U17" t="s">
         <v>29</v>
@@ -2641,7 +2620,7 @@
         <v>27</v>
       </c>
       <c r="W17" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.3">
@@ -2649,10 +2628,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="C18" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="D18" t="s">
         <v>23</v>
@@ -2664,19 +2643,19 @@
         <v>24</v>
       </c>
       <c r="L18" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="M18" t="s">
         <v>25</v>
       </c>
       <c r="N18" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="O18" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="P18" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="Q18" t="s">
         <v>28</v>
@@ -2685,10 +2664,10 @@
         <v>1</v>
       </c>
       <c r="S18" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T18" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="U18" t="s">
         <v>29</v>
@@ -2697,7 +2676,7 @@
         <v>27</v>
       </c>
       <c r="W18" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.3">
@@ -2705,10 +2684,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="C19" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="D19" t="s">
         <v>23</v>
@@ -2720,19 +2699,19 @@
         <v>24</v>
       </c>
       <c r="L19" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="M19" t="s">
         <v>25</v>
       </c>
       <c r="N19" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="O19" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="P19" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="Q19" t="s">
         <v>28</v>
@@ -2741,10 +2720,10 @@
         <v>1</v>
       </c>
       <c r="S19" t="s">
-        <v>182</v>
+        <v>49</v>
       </c>
       <c r="T19" t="s">
-        <v>31</v>
+        <v>170</v>
       </c>
       <c r="U19" t="s">
         <v>29</v>
@@ -2753,7 +2732,7 @@
         <v>27</v>
       </c>
       <c r="W19" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.3">
@@ -2761,10 +2740,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="C20" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D20" t="s">
         <v>23</v>
@@ -2776,19 +2755,19 @@
         <v>24</v>
       </c>
       <c r="L20" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="M20" t="s">
         <v>25</v>
       </c>
       <c r="N20" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="O20" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="P20" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="Q20" t="s">
         <v>28</v>
@@ -2797,10 +2776,10 @@
         <v>1</v>
       </c>
       <c r="S20" t="s">
-        <v>43</v>
+        <v>404</v>
       </c>
       <c r="T20" t="s">
-        <v>190</v>
+        <v>30</v>
       </c>
       <c r="U20" t="s">
         <v>29</v>
@@ -2809,7 +2788,7 @@
         <v>27</v>
       </c>
       <c r="W20" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.3">
@@ -2817,10 +2796,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="C21" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="D21" t="s">
         <v>23</v>
@@ -2832,19 +2811,19 @@
         <v>24</v>
       </c>
       <c r="L21" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="M21" t="s">
         <v>25</v>
       </c>
       <c r="N21" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="O21" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="P21" t="s">
-        <v>35</v>
+        <v>184</v>
       </c>
       <c r="Q21" t="s">
         <v>28</v>
@@ -2853,10 +2832,10 @@
         <v>1</v>
       </c>
       <c r="S21" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="T21" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="U21" t="s">
         <v>29</v>
@@ -2865,7 +2844,7 @@
         <v>27</v>
       </c>
       <c r="W21" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.3">
@@ -2873,10 +2852,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="C22" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="D22" t="s">
         <v>23</v>
@@ -2888,19 +2867,19 @@
         <v>24</v>
       </c>
       <c r="L22" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="M22" t="s">
         <v>25</v>
       </c>
       <c r="N22" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="O22" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="P22" t="s">
-        <v>204</v>
+        <v>34</v>
       </c>
       <c r="Q22" t="s">
         <v>28</v>
@@ -2909,10 +2888,10 @@
         <v>1</v>
       </c>
       <c r="S22" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="T22" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="U22" t="s">
         <v>29</v>
@@ -2921,7 +2900,7 @@
         <v>27</v>
       </c>
       <c r="W22" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.3">
@@ -2929,10 +2908,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="C23" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="D23" t="s">
         <v>23</v>
@@ -2944,19 +2923,19 @@
         <v>24</v>
       </c>
       <c r="L23" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="M23" t="s">
         <v>25</v>
       </c>
       <c r="N23" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="O23" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="P23" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="Q23" t="s">
         <v>28</v>
@@ -2965,10 +2944,10 @@
         <v>1</v>
       </c>
       <c r="S23" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="T23" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="U23" t="s">
         <v>29</v>
@@ -2977,7 +2956,7 @@
         <v>27</v>
       </c>
       <c r="W23" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.3">
@@ -2985,10 +2964,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="C24" t="s">
-        <v>137</v>
+        <v>203</v>
       </c>
       <c r="D24" t="s">
         <v>23</v>
@@ -3000,19 +2979,19 @@
         <v>24</v>
       </c>
       <c r="L24" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="M24" t="s">
         <v>25</v>
       </c>
       <c r="N24" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="O24" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="P24" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="Q24" t="s">
         <v>28</v>
@@ -3021,10 +3000,10 @@
         <v>1</v>
       </c>
       <c r="S24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T24" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="U24" t="s">
         <v>29</v>
@@ -3033,7 +3012,7 @@
         <v>27</v>
       </c>
       <c r="W24" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.3">
@@ -3041,10 +3020,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="C25" t="s">
-        <v>223</v>
+        <v>133</v>
       </c>
       <c r="D25" t="s">
         <v>23</v>
@@ -3056,19 +3035,19 @@
         <v>24</v>
       </c>
       <c r="L25" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="M25" t="s">
         <v>25</v>
       </c>
       <c r="N25" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="O25" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="P25" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="Q25" t="s">
         <v>28</v>
@@ -3077,10 +3056,10 @@
         <v>1</v>
       </c>
       <c r="S25" t="s">
-        <v>228</v>
+        <v>49</v>
       </c>
       <c r="T25" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="U25" t="s">
         <v>29</v>
@@ -3089,7 +3068,7 @@
         <v>27</v>
       </c>
       <c r="W25" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.3">
@@ -3097,10 +3076,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="C26" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="D26" t="s">
         <v>23</v>
@@ -3112,19 +3091,19 @@
         <v>24</v>
       </c>
       <c r="L26" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="M26" t="s">
         <v>25</v>
       </c>
       <c r="N26" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="O26" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="P26" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="Q26" t="s">
         <v>28</v>
@@ -3133,10 +3112,10 @@
         <v>1</v>
       </c>
       <c r="S26" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T26" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="U26" t="s">
         <v>29</v>
@@ -3145,7 +3124,7 @@
         <v>27</v>
       </c>
       <c r="W26" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.3">
@@ -3153,10 +3132,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="C27" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="D27" t="s">
         <v>23</v>
@@ -3168,19 +3147,19 @@
         <v>24</v>
       </c>
       <c r="L27" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="M27" t="s">
         <v>25</v>
       </c>
       <c r="N27" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="O27" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="P27" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="Q27" t="s">
         <v>28</v>
@@ -3189,10 +3168,10 @@
         <v>1</v>
       </c>
       <c r="S27" t="s">
-        <v>43</v>
+        <v>405</v>
       </c>
       <c r="T27" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="U27" t="s">
         <v>29</v>
@@ -3201,7 +3180,7 @@
         <v>27</v>
       </c>
       <c r="W27" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.3">
@@ -3209,10 +3188,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="C28" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D28" t="s">
         <v>23</v>
@@ -3224,19 +3203,19 @@
         <v>24</v>
       </c>
       <c r="L28" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="M28" t="s">
         <v>25</v>
       </c>
       <c r="N28" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="O28" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P28" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="Q28" t="s">
         <v>28</v>
@@ -3245,10 +3224,10 @@
         <v>1</v>
       </c>
       <c r="S28" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T28" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="U28" t="s">
         <v>29</v>
@@ -3257,7 +3236,7 @@
         <v>27</v>
       </c>
       <c r="W28" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.3">
@@ -3265,10 +3244,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="C29" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="D29" t="s">
         <v>23</v>
@@ -3280,19 +3259,19 @@
         <v>24</v>
       </c>
       <c r="L29" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="M29" t="s">
         <v>25</v>
       </c>
       <c r="N29" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="O29" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="P29" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="Q29" t="s">
         <v>28</v>
@@ -3301,10 +3280,10 @@
         <v>1</v>
       </c>
       <c r="S29" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T29" t="s">
-        <v>36</v>
+        <v>247</v>
       </c>
       <c r="U29" t="s">
         <v>29</v>
@@ -3313,7 +3292,7 @@
         <v>27</v>
       </c>
       <c r="W29" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.3">
@@ -3321,10 +3300,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="C30" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="D30" t="s">
         <v>23</v>
@@ -3336,19 +3315,19 @@
         <v>24</v>
       </c>
       <c r="L30" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="M30" t="s">
         <v>25</v>
       </c>
       <c r="N30" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="O30" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="P30" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="Q30" t="s">
         <v>28</v>
@@ -3357,10 +3336,10 @@
         <v>1</v>
       </c>
       <c r="S30" t="s">
-        <v>268</v>
+        <v>49</v>
       </c>
       <c r="T30" t="s">
-        <v>269</v>
+        <v>35</v>
       </c>
       <c r="U30" t="s">
         <v>29</v>
@@ -3369,7 +3348,7 @@
         <v>27</v>
       </c>
       <c r="W30" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.3">
@@ -3377,10 +3356,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="C31" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="D31" t="s">
         <v>23</v>
@@ -3392,19 +3371,19 @@
         <v>24</v>
       </c>
       <c r="L31" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="M31" t="s">
         <v>25</v>
       </c>
       <c r="N31" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="O31" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="P31" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="Q31" t="s">
         <v>28</v>
@@ -3413,10 +3392,10 @@
         <v>1</v>
       </c>
       <c r="S31" t="s">
-        <v>277</v>
+        <v>49</v>
       </c>
       <c r="T31" t="s">
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="U31" t="s">
         <v>29</v>
@@ -3425,7 +3404,7 @@
         <v>27</v>
       </c>
       <c r="W31" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.3">
@@ -3433,10 +3412,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>280</v>
+        <v>264</v>
       </c>
       <c r="C32" t="s">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="D32" t="s">
         <v>23</v>
@@ -3448,19 +3427,19 @@
         <v>24</v>
       </c>
       <c r="L32" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="M32" t="s">
         <v>25</v>
       </c>
       <c r="N32" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="O32" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="P32" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="Q32" t="s">
         <v>28</v>
@@ -3469,10 +3448,10 @@
         <v>1</v>
       </c>
       <c r="S32" t="s">
-        <v>285</v>
+        <v>49</v>
       </c>
       <c r="T32" t="s">
-        <v>286</v>
+        <v>270</v>
       </c>
       <c r="U32" t="s">
         <v>29</v>
@@ -3481,7 +3460,7 @@
         <v>27</v>
       </c>
       <c r="W32" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.3">
@@ -3489,10 +3468,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="C33" t="s">
-        <v>289</v>
+        <v>234</v>
       </c>
       <c r="D33" t="s">
         <v>23</v>
@@ -3504,19 +3483,19 @@
         <v>24</v>
       </c>
       <c r="L33" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="M33" t="s">
         <v>25</v>
       </c>
       <c r="N33" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="O33" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="P33" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="Q33" t="s">
         <v>28</v>
@@ -3525,10 +3504,10 @@
         <v>1</v>
       </c>
       <c r="S33" t="s">
-        <v>294</v>
+        <v>49</v>
       </c>
       <c r="T33" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="U33" t="s">
         <v>29</v>
@@ -3537,7 +3516,7 @@
         <v>27</v>
       </c>
       <c r="W33" t="s">
-        <v>296</v>
+        <v>278</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.3">
@@ -3545,10 +3524,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="C34" t="s">
-        <v>298</v>
+        <v>280</v>
       </c>
       <c r="D34" t="s">
         <v>23</v>
@@ -3560,19 +3539,19 @@
         <v>24</v>
       </c>
       <c r="L34" t="s">
-        <v>299</v>
+        <v>281</v>
       </c>
       <c r="M34" t="s">
         <v>25</v>
       </c>
       <c r="N34" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="O34" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="P34" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="Q34" t="s">
         <v>28</v>
@@ -3581,10 +3560,10 @@
         <v>1</v>
       </c>
       <c r="S34" t="s">
-        <v>303</v>
+        <v>49</v>
       </c>
       <c r="T34" t="s">
-        <v>304</v>
+        <v>285</v>
       </c>
       <c r="U34" t="s">
         <v>29</v>
@@ -3593,7 +3572,7 @@
         <v>27</v>
       </c>
       <c r="W34" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.3">
@@ -3601,10 +3580,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="C35" t="s">
-        <v>263</v>
+        <v>288</v>
       </c>
       <c r="D35" t="s">
         <v>23</v>
@@ -3616,19 +3595,19 @@
         <v>24</v>
       </c>
       <c r="L35" t="s">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="M35" t="s">
         <v>25</v>
       </c>
       <c r="N35" t="s">
-        <v>308</v>
+        <v>290</v>
       </c>
       <c r="O35" t="s">
-        <v>309</v>
+        <v>291</v>
       </c>
       <c r="P35" t="s">
-        <v>310</v>
+        <v>292</v>
       </c>
       <c r="Q35" t="s">
         <v>28</v>
@@ -3637,10 +3616,10 @@
         <v>1</v>
       </c>
       <c r="S35" t="s">
-        <v>311</v>
+        <v>49</v>
       </c>
       <c r="T35" t="s">
-        <v>312</v>
+        <v>293</v>
       </c>
       <c r="U35" t="s">
         <v>29</v>
@@ -3649,7 +3628,7 @@
         <v>27</v>
       </c>
       <c r="W35" t="s">
-        <v>313</v>
+        <v>294</v>
       </c>
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.3">
@@ -3657,10 +3636,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>314</v>
+        <v>295</v>
       </c>
       <c r="C36" t="s">
-        <v>315</v>
+        <v>257</v>
       </c>
       <c r="D36" t="s">
         <v>23</v>
@@ -3672,31 +3651,28 @@
         <v>24</v>
       </c>
       <c r="L36" t="s">
-        <v>316</v>
+        <v>296</v>
       </c>
       <c r="M36" t="s">
         <v>25</v>
       </c>
       <c r="N36" t="s">
-        <v>317</v>
+        <v>297</v>
       </c>
       <c r="O36" t="s">
-        <v>318</v>
+        <v>298</v>
       </c>
       <c r="P36" t="s">
-        <v>319</v>
+        <v>299</v>
       </c>
       <c r="Q36" t="s">
         <v>28</v>
       </c>
       <c r="R36" t="b">
-        <v>1</v>
-      </c>
-      <c r="S36" t="s">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="T36" t="s">
-        <v>321</v>
+        <v>300</v>
       </c>
       <c r="U36" t="s">
         <v>29</v>
@@ -3705,7 +3681,7 @@
         <v>27</v>
       </c>
       <c r="W36" t="s">
-        <v>322</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.3">
@@ -3713,10 +3689,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>323</v>
+        <v>302</v>
       </c>
       <c r="C37" t="s">
-        <v>324</v>
+        <v>303</v>
       </c>
       <c r="D37" t="s">
         <v>23</v>
@@ -3728,31 +3704,28 @@
         <v>24</v>
       </c>
       <c r="L37" t="s">
-        <v>325</v>
+        <v>304</v>
       </c>
       <c r="M37" t="s">
         <v>25</v>
       </c>
       <c r="N37" t="s">
-        <v>326</v>
+        <v>305</v>
       </c>
       <c r="O37" t="s">
-        <v>327</v>
+        <v>306</v>
       </c>
       <c r="P37" t="s">
-        <v>328</v>
+        <v>307</v>
       </c>
       <c r="Q37" t="s">
         <v>28</v>
       </c>
       <c r="R37" t="b">
-        <v>1</v>
-      </c>
-      <c r="S37" t="s">
-        <v>329</v>
+        <v>0</v>
       </c>
       <c r="T37" t="s">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="U37" t="s">
         <v>29</v>
@@ -3761,7 +3734,7 @@
         <v>27</v>
       </c>
       <c r="W37" t="s">
-        <v>331</v>
+        <v>309</v>
       </c>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.3">
@@ -3769,10 +3742,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>332</v>
+        <v>310</v>
       </c>
       <c r="C38" t="s">
-        <v>333</v>
+        <v>311</v>
       </c>
       <c r="D38" t="s">
         <v>23</v>
@@ -3784,31 +3757,28 @@
         <v>24</v>
       </c>
       <c r="L38" t="s">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="M38" t="s">
         <v>25</v>
       </c>
       <c r="N38" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="O38" t="s">
-        <v>336</v>
+        <v>314</v>
       </c>
       <c r="P38" t="s">
-        <v>337</v>
+        <v>315</v>
       </c>
       <c r="Q38" t="s">
         <v>28</v>
       </c>
       <c r="R38" t="b">
-        <v>1</v>
-      </c>
-      <c r="S38" t="s">
-        <v>338</v>
+        <v>0</v>
       </c>
       <c r="T38" t="s">
-        <v>339</v>
+        <v>316</v>
       </c>
       <c r="U38" t="s">
         <v>29</v>
@@ -3817,7 +3787,7 @@
         <v>27</v>
       </c>
       <c r="W38" t="s">
-        <v>340</v>
+        <v>317</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.3">
@@ -3825,10 +3795,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>341</v>
+        <v>318</v>
       </c>
       <c r="C39" t="s">
-        <v>232</v>
+        <v>319</v>
       </c>
       <c r="D39" t="s">
         <v>23</v>
@@ -3840,19 +3810,19 @@
         <v>24</v>
       </c>
       <c r="L39" t="s">
-        <v>342</v>
+        <v>320</v>
       </c>
       <c r="M39" t="s">
         <v>25</v>
       </c>
       <c r="N39" t="s">
-        <v>343</v>
+        <v>321</v>
       </c>
       <c r="O39" t="s">
-        <v>344</v>
+        <v>322</v>
       </c>
       <c r="P39" t="s">
-        <v>345</v>
+        <v>323</v>
       </c>
       <c r="Q39" t="s">
         <v>28</v>
@@ -3861,10 +3831,10 @@
         <v>1</v>
       </c>
       <c r="S39" t="s">
-        <v>320</v>
+        <v>403</v>
       </c>
       <c r="T39" t="s">
-        <v>346</v>
+        <v>324</v>
       </c>
       <c r="U39" t="s">
         <v>29</v>
@@ -3873,7 +3843,7 @@
         <v>27</v>
       </c>
       <c r="W39" t="s">
-        <v>347</v>
+        <v>325</v>
       </c>
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.3">
@@ -3881,10 +3851,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="C40" t="s">
-        <v>349</v>
+        <v>226</v>
       </c>
       <c r="D40" t="s">
         <v>23</v>
@@ -3896,31 +3866,28 @@
         <v>24</v>
       </c>
       <c r="L40" t="s">
-        <v>350</v>
+        <v>327</v>
       </c>
       <c r="M40" t="s">
         <v>25</v>
       </c>
       <c r="N40" t="s">
-        <v>351</v>
+        <v>328</v>
       </c>
       <c r="O40" t="s">
-        <v>352</v>
+        <v>329</v>
       </c>
       <c r="P40" t="s">
-        <v>353</v>
+        <v>330</v>
       </c>
       <c r="Q40" t="s">
         <v>28</v>
       </c>
       <c r="R40" t="b">
-        <v>1</v>
-      </c>
-      <c r="S40" t="s">
-        <v>354</v>
+        <v>0</v>
       </c>
       <c r="T40" t="s">
-        <v>355</v>
+        <v>331</v>
       </c>
       <c r="U40" t="s">
         <v>29</v>
@@ -3929,7 +3896,7 @@
         <v>27</v>
       </c>
       <c r="W40" t="s">
-        <v>356</v>
+        <v>332</v>
       </c>
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.3">
@@ -3937,10 +3904,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>357</v>
+        <v>333</v>
       </c>
       <c r="C41" t="s">
-        <v>358</v>
+        <v>334</v>
       </c>
       <c r="D41" t="s">
         <v>23</v>
@@ -3952,31 +3919,28 @@
         <v>24</v>
       </c>
       <c r="L41" t="s">
-        <v>359</v>
+        <v>335</v>
       </c>
       <c r="M41" t="s">
         <v>25</v>
       </c>
       <c r="N41" t="s">
-        <v>360</v>
+        <v>336</v>
       </c>
       <c r="O41" t="s">
-        <v>361</v>
+        <v>337</v>
       </c>
       <c r="P41" t="s">
-        <v>362</v>
+        <v>338</v>
       </c>
       <c r="Q41" t="s">
         <v>28</v>
       </c>
       <c r="R41" t="b">
-        <v>1</v>
-      </c>
-      <c r="S41" t="s">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="T41" t="s">
-        <v>363</v>
+        <v>339</v>
       </c>
       <c r="U41" t="s">
         <v>29</v>
@@ -3985,7 +3949,7 @@
         <v>27</v>
       </c>
       <c r="W41" t="s">
-        <v>364</v>
+        <v>340</v>
       </c>
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.3">
@@ -3993,10 +3957,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>365</v>
+        <v>341</v>
       </c>
       <c r="C42" t="s">
-        <v>366</v>
+        <v>342</v>
       </c>
       <c r="D42" t="s">
         <v>23</v>
@@ -4008,31 +3972,28 @@
         <v>24</v>
       </c>
       <c r="L42" t="s">
-        <v>367</v>
+        <v>343</v>
       </c>
       <c r="M42" t="s">
         <v>25</v>
       </c>
       <c r="N42" t="s">
-        <v>368</v>
+        <v>344</v>
       </c>
       <c r="O42" t="s">
-        <v>369</v>
+        <v>345</v>
       </c>
       <c r="P42" t="s">
-        <v>370</v>
+        <v>346</v>
       </c>
       <c r="Q42" t="s">
         <v>28</v>
       </c>
       <c r="R42" t="b">
-        <v>1</v>
-      </c>
-      <c r="S42" t="s">
-        <v>329</v>
+        <v>0</v>
       </c>
       <c r="T42" t="s">
-        <v>371</v>
+        <v>347</v>
       </c>
       <c r="U42" t="s">
         <v>29</v>
@@ -4041,7 +4002,7 @@
         <v>27</v>
       </c>
       <c r="W42" t="s">
-        <v>372</v>
+        <v>348</v>
       </c>
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.3">
@@ -4049,10 +4010,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
       <c r="C43" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
       <c r="D43" t="s">
         <v>23</v>
@@ -4064,31 +4025,28 @@
         <v>24</v>
       </c>
       <c r="L43" t="s">
-        <v>375</v>
+        <v>351</v>
       </c>
       <c r="M43" t="s">
         <v>25</v>
       </c>
       <c r="N43" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
       <c r="O43" t="s">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c r="P43" t="s">
-        <v>378</v>
+        <v>354</v>
       </c>
       <c r="Q43" t="s">
         <v>28</v>
       </c>
       <c r="R43" t="b">
-        <v>1</v>
-      </c>
-      <c r="S43" t="s">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="T43" t="s">
-        <v>379</v>
+        <v>355</v>
       </c>
       <c r="U43" t="s">
         <v>29</v>
@@ -4097,7 +4055,7 @@
         <v>27</v>
       </c>
       <c r="W43" t="s">
-        <v>380</v>
+        <v>356</v>
       </c>
     </row>
     <row r="44" spans="1:23" x14ac:dyDescent="0.3">
@@ -4105,10 +4063,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>381</v>
+        <v>357</v>
       </c>
       <c r="C44" t="s">
-        <v>382</v>
+        <v>358</v>
       </c>
       <c r="D44" t="s">
         <v>23</v>
@@ -4120,31 +4078,28 @@
         <v>24</v>
       </c>
       <c r="L44" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="M44" t="s">
         <v>25</v>
       </c>
       <c r="N44" t="s">
-        <v>384</v>
+        <v>360</v>
       </c>
       <c r="O44" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="P44" t="s">
-        <v>386</v>
+        <v>362</v>
       </c>
       <c r="Q44" t="s">
         <v>28</v>
       </c>
       <c r="R44" t="b">
-        <v>1</v>
-      </c>
-      <c r="S44" t="s">
-        <v>387</v>
+        <v>0</v>
       </c>
       <c r="T44" t="s">
-        <v>388</v>
+        <v>363</v>
       </c>
       <c r="U44" t="s">
         <v>29</v>
@@ -4153,7 +4108,7 @@
         <v>27</v>
       </c>
       <c r="W44" t="s">
-        <v>389</v>
+        <v>364</v>
       </c>
     </row>
     <row r="45" spans="1:23" x14ac:dyDescent="0.3">
@@ -4161,10 +4116,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>390</v>
+        <v>365</v>
       </c>
       <c r="C45" t="s">
-        <v>391</v>
+        <v>366</v>
       </c>
       <c r="D45" t="s">
         <v>23</v>
@@ -4176,31 +4131,28 @@
         <v>24</v>
       </c>
       <c r="L45" t="s">
-        <v>392</v>
+        <v>367</v>
       </c>
       <c r="M45" t="s">
         <v>25</v>
       </c>
       <c r="N45" t="s">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="O45" t="s">
-        <v>394</v>
+        <v>369</v>
       </c>
       <c r="P45" t="s">
-        <v>395</v>
+        <v>370</v>
       </c>
       <c r="Q45" t="s">
         <v>28</v>
       </c>
       <c r="R45" t="b">
-        <v>1</v>
-      </c>
-      <c r="S45" t="s">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="T45" t="s">
-        <v>37</v>
+        <v>371</v>
       </c>
       <c r="U45" t="s">
         <v>29</v>
@@ -4209,7 +4161,7 @@
         <v>27</v>
       </c>
       <c r="W45" t="s">
-        <v>397</v>
+        <v>372</v>
       </c>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.3">
@@ -4217,10 +4169,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>398</v>
+        <v>373</v>
       </c>
       <c r="C46" t="s">
-        <v>32</v>
+        <v>374</v>
       </c>
       <c r="D46" t="s">
         <v>23</v>
@@ -4232,31 +4184,28 @@
         <v>24</v>
       </c>
       <c r="L46" t="s">
-        <v>399</v>
+        <v>375</v>
       </c>
       <c r="M46" t="s">
         <v>25</v>
       </c>
       <c r="N46" t="s">
-        <v>400</v>
+        <v>376</v>
       </c>
       <c r="O46" t="s">
-        <v>401</v>
+        <v>377</v>
       </c>
       <c r="P46" t="s">
-        <v>402</v>
+        <v>378</v>
       </c>
       <c r="Q46" t="s">
         <v>28</v>
       </c>
       <c r="R46" t="b">
-        <v>1</v>
-      </c>
-      <c r="S46" t="s">
-        <v>329</v>
+        <v>0</v>
       </c>
       <c r="T46" t="s">
-        <v>403</v>
+        <v>36</v>
       </c>
       <c r="U46" t="s">
         <v>29</v>
@@ -4265,7 +4214,7 @@
         <v>27</v>
       </c>
       <c r="W46" t="s">
-        <v>404</v>
+        <v>379</v>
       </c>
     </row>
     <row r="47" spans="1:23" x14ac:dyDescent="0.3">
@@ -4273,10 +4222,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>405</v>
+        <v>380</v>
       </c>
       <c r="C47" t="s">
-        <v>406</v>
+        <v>31</v>
       </c>
       <c r="D47" t="s">
         <v>23</v>
@@ -4288,19 +4237,19 @@
         <v>24</v>
       </c>
       <c r="L47" t="s">
-        <v>407</v>
+        <v>381</v>
       </c>
       <c r="M47" t="s">
         <v>25</v>
       </c>
       <c r="N47" t="s">
-        <v>408</v>
+        <v>382</v>
       </c>
       <c r="O47" t="s">
-        <v>409</v>
+        <v>383</v>
       </c>
       <c r="P47" t="s">
-        <v>410</v>
+        <v>384</v>
       </c>
       <c r="Q47" t="s">
         <v>28</v>
@@ -4309,10 +4258,10 @@
         <v>1</v>
       </c>
       <c r="S47" t="s">
-        <v>320</v>
+        <v>403</v>
       </c>
       <c r="T47" t="s">
-        <v>411</v>
+        <v>385</v>
       </c>
       <c r="U47" t="s">
         <v>29</v>
@@ -4321,7 +4270,7 @@
         <v>27</v>
       </c>
       <c r="W47" t="s">
-        <v>412</v>
+        <v>386</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.3">
@@ -4329,10 +4278,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>413</v>
+        <v>387</v>
       </c>
       <c r="C48" t="s">
-        <v>414</v>
+        <v>388</v>
       </c>
       <c r="D48" t="s">
         <v>23</v>
@@ -4344,31 +4293,28 @@
         <v>24</v>
       </c>
       <c r="L48" t="s">
-        <v>415</v>
+        <v>389</v>
       </c>
       <c r="M48" t="s">
         <v>25</v>
       </c>
       <c r="N48" t="s">
-        <v>416</v>
+        <v>390</v>
       </c>
       <c r="O48" t="s">
-        <v>417</v>
+        <v>391</v>
       </c>
       <c r="P48" t="s">
-        <v>418</v>
+        <v>392</v>
       </c>
       <c r="Q48" t="s">
         <v>28</v>
       </c>
       <c r="R48" t="b">
-        <v>1</v>
-      </c>
-      <c r="S48" t="s">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="T48" t="s">
-        <v>419</v>
+        <v>393</v>
       </c>
       <c r="U48" t="s">
         <v>29</v>
@@ -4377,7 +4323,60 @@
         <v>27</v>
       </c>
       <c r="W48" t="s">
-        <v>420</v>
+        <v>394</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>395</v>
+      </c>
+      <c r="C49" t="s">
+        <v>396</v>
+      </c>
+      <c r="D49" t="s">
+        <v>23</v>
+      </c>
+      <c r="J49" t="s">
+        <v>24</v>
+      </c>
+      <c r="K49" t="s">
+        <v>24</v>
+      </c>
+      <c r="L49" t="s">
+        <v>397</v>
+      </c>
+      <c r="M49" t="s">
+        <v>25</v>
+      </c>
+      <c r="N49" t="s">
+        <v>398</v>
+      </c>
+      <c r="O49" t="s">
+        <v>399</v>
+      </c>
+      <c r="P49" t="s">
+        <v>400</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>28</v>
+      </c>
+      <c r="R49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="s">
+        <v>401</v>
+      </c>
+      <c r="U49" t="s">
+        <v>29</v>
+      </c>
+      <c r="V49" t="s">
+        <v>27</v>
+      </c>
+      <c r="W49" t="s">
+        <v>402</v>
       </c>
     </row>
   </sheetData>
